--- a/output/pdf_financials_xlsx/REE.xlsx
+++ b/output/pdf_financials_xlsx/REE.xlsx
@@ -883,13 +883,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.007125</v>
+        <v>-0.007125</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.075599</v>
+        <v>-0.075599</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.029874</v>
+        <v>-0.029874</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-0.20143</v>
@@ -1039,13 +1039,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.007125</v>
+        <v>-0.007125</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.075599</v>
+        <v>-0.075599</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.029874</v>
+        <v>-0.029874</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-0.20143</v>
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.007125</v>
+        <v>-0.007125</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.075599</v>
+        <v>-0.075599</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.029874</v>
+        <v>-0.029874</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-0.20143</v>
@@ -1268,13 +1268,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.007125</v>
+        <v>-0.007125</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.075599</v>
+        <v>-0.075599</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.029874</v>
+        <v>-0.029874</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-0.20143</v>
@@ -1330,13 +1330,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.007125</v>
+        <v>-0.007125</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.075599</v>
+        <v>-0.075599</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.029874</v>
+        <v>-0.029874</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.20143</v>
@@ -1408,13 +1408,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -10449,10 +10449,10 @@
         </is>
       </c>
       <c r="F104" s="5" t="n">
-        <v>0.075599</v>
+        <v>-0.075599</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.029874</v>
+        <v>-0.029874</v>
       </c>
       <c r="H104" s="5" t="n">
         <v>-0.20143</v>
@@ -11872,10 +11872,10 @@
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>0.007125</v>
+        <v>-0.007125</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>0.075599</v>
+        <v>-0.075599</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/REE.xlsx
+++ b/output/pdf_financials_xlsx/REE.xlsx
@@ -1493,13 +1493,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.680736</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.641329</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0.05538</v>
@@ -1555,13 +1555,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.680736</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.641329</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0.05538</v>
@@ -1927,13 +1927,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.684723</v>
+        <v>0.003987</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.645316</v>
+        <v>0.003987</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">

--- a/output/pdf_financials_xlsx/REE.xlsx
+++ b/output/pdf_financials_xlsx/REE.xlsx
@@ -2460,19 +2460,19 @@
         <v>0</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.109705</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.322245</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.235753</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.17524</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.272044</v>
       </c>
     </row>
     <row r="65">
@@ -3947,19 +3947,19 @@
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.016561</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.030718</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.060027</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.012</v>
       </c>
     </row>
     <row r="112">
@@ -4694,19 +4694,19 @@
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.016561</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.030718</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.060027</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.012</v>
       </c>
     </row>
     <row r="135">
@@ -4725,10 +4725,10 @@
         <v>-0.039407</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.159544</v>
+        <v>-0.176105</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-1.253839</v>
+        <v>-1.284557</v>
       </c>
       <c r="G135" s="1" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>-0.43511</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-0.192812</v>
+        <v>-0.204812</v>
       </c>
     </row>
   </sheetData>
@@ -7374,7 +7374,11 @@
           <t>Purchases of equipment</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
